--- a/tests/MaterialLibrary.Examples/Demo.xlsx
+++ b/tests/MaterialLibrary.Examples/Demo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ganfossi\Documents\Codes\F#\Materials\tests\MaterialLibrary.Examples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{782E3850-2435-4813-840E-2947664F788D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F58E05B9-848D-4E8E-AD36-F82E0EF5C774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{14284A69-5191-496A-850C-9A40DA964F84}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -431,7 +431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA3E2D39-1E75-49F3-BEB7-624844DD738A}">
-  <dimension ref="D5:P34"/>
+  <dimension ref="D5:M21"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="13.69921875" customWidth="1"/>
@@ -446,441 +446,51 @@
     <col min="16" max="16" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="D5" t="str" cm="1">
-        <f t="array" ref="D5">_xll.MatOpenDatabase("C:\Users\ganfossi\Documents\DataBase\data\asme_materials.db")</f>
-        <v>Loaded 2129 materials from the ASME database.</v>
-      </c>
-    </row>
-    <row r="6" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="D6" t="str" cm="1">
-        <f t="array" ref="D6">_xll.MatDefaultAsmeDatabasePath()</f>
-        <v>C:\Users\ganfossi\Documents\DataBase\data\asme_materials.db</v>
-      </c>
-    </row>
-    <row r="7" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="D7" t="str" cm="1">
-        <f t="array" ref="D7">_xll.MatConfigPath()</f>
-        <v>MaterialLibrary.config.xml</v>
-      </c>
-    </row>
-    <row r="8" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="D8" t="str" cm="1">
-        <f t="array" ref="D8">_xll.status()</f>
-        <v>Database: C:\Users\ganfossi\Documents\DataBase\data\asme_materials.db (2129 materials) | JSON library: not loaded | Combined: 2129 materials</v>
-      </c>
-    </row>
-    <row r="9" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="D9" t="str" cm="1">
-        <f t="array" ref="D9">_xll.MatSaveMaterial("ASME-177","C:\Users\ganfossi\Documents")</f>
-        <v>#VALUE! File write failed: Access to the path 'C:\Users\ganfossi\Documents' is denied.</v>
-      </c>
-    </row>
-    <row r="10" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D5" t="e" cm="1">
+        <f t="array" aca="1" ref="D5" ca="1">_xll.MatOpenDatabase("C:\Users\ganfossi\Documents\DataBase\data\asme_materials.db")</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="6" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D6" t="e" cm="1">
+        <f t="array" aca="1" ref="D6" ca="1">_xll.MatDefaultAsmeDatabasePath()</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="7" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D7" t="e" cm="1">
+        <f t="array" aca="1" ref="D7" ca="1">_xll.MatConfigPath()</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="8" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D8" t="e" cm="1">
+        <f t="array" aca="1" ref="D8" ca="1">_xll.status()</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="10" spans="4:13" x14ac:dyDescent="0.3">
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
     </row>
-    <row r="13" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="D13" s="1" t="str" cm="1">
-        <f t="array" ref="D13:I17">_xll.MatSearch("SA-516")</f>
-        <v>Id</v>
-      </c>
-      <c r="E13" t="str">
-        <v>Name</v>
-      </c>
-      <c r="F13" t="str">
-        <v>Specification</v>
-      </c>
-      <c r="G13" t="str">
-        <v>Grade</v>
-      </c>
-      <c r="H13" t="str">
-        <v>Family</v>
-      </c>
-      <c r="I13" t="str">
-        <v>ProductForm</v>
-      </c>
-      <c r="M13" t="str" cm="1">
-        <f t="array" ref="M13:P34">_xll.MatAllowableStressTable("ASME-355","Bolting")</f>
-        <v>Temperature_degC</v>
-      </c>
-      <c r="N13" t="str">
-        <v>100.000 - 180.000 mm</v>
-      </c>
-      <c r="O13" t="str">
-        <v>64.000 - 100.000 mm</v>
-      </c>
-      <c r="P13" t="str">
-        <v>&lt;= 64.000 mm</v>
-      </c>
-    </row>
-    <row r="14" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="D14" t="str">
-        <v>ASME-126</v>
-      </c>
-      <c r="E14" t="str">
-        <v>SA-516 65 K02403</v>
-      </c>
-      <c r="F14" t="str">
-        <v>SA-516</v>
-      </c>
-      <c r="G14" t="str">
-        <v>65</v>
-      </c>
-      <c r="H14" t="str">
-        <v>CS</v>
-      </c>
-      <c r="I14" t="str">
-        <v>Plate</v>
-      </c>
-      <c r="M14">
-        <v>40</v>
-      </c>
-      <c r="N14">
-        <v>130</v>
-      </c>
-      <c r="O14">
-        <v>159</v>
-      </c>
-      <c r="P14">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="15" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="D15" t="str">
-        <v>ASME-177</v>
-      </c>
-      <c r="E15" t="str">
-        <v>SA-516 70 K02700</v>
-      </c>
-      <c r="F15" t="str">
-        <v>SA-516</v>
-      </c>
-      <c r="G15" t="str">
-        <v>70</v>
-      </c>
-      <c r="H15" t="str">
-        <v>CS</v>
-      </c>
-      <c r="I15" t="str">
-        <v>Plate</v>
-      </c>
-      <c r="M15">
-        <v>65</v>
-      </c>
-      <c r="N15">
-        <v>130</v>
-      </c>
-      <c r="O15">
-        <v>159</v>
-      </c>
-      <c r="P15">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="16" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="D16" t="str">
-        <v>ASME-41</v>
-      </c>
-      <c r="E16" t="str">
-        <v>SA-516 55 K01800</v>
-      </c>
-      <c r="F16" t="str">
-        <v>SA-516</v>
-      </c>
-      <c r="G16" t="str">
-        <v>55</v>
-      </c>
-      <c r="H16" t="str">
-        <v>CS</v>
-      </c>
-      <c r="I16" t="str">
-        <v>Plate</v>
-      </c>
-      <c r="M16">
-        <v>100</v>
-      </c>
-      <c r="N16">
-        <v>130</v>
-      </c>
-      <c r="O16">
-        <v>159</v>
-      </c>
-      <c r="P16">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="17" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="D17" t="str">
-        <v>ASME-83</v>
-      </c>
-      <c r="E17" t="str">
-        <v>SA-516 60 K02100</v>
-      </c>
-      <c r="F17" t="str">
-        <v>SA-516</v>
-      </c>
-      <c r="G17" t="str">
-        <v>60</v>
-      </c>
-      <c r="H17" t="str">
-        <v>CS</v>
-      </c>
-      <c r="I17" t="str">
-        <v>Plate</v>
-      </c>
-      <c r="M17">
-        <v>125</v>
-      </c>
-      <c r="N17">
-        <v>130</v>
-      </c>
-      <c r="O17">
-        <v>159</v>
-      </c>
-      <c r="P17">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="18" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="M18">
-        <v>150</v>
-      </c>
-      <c r="N18">
-        <v>130</v>
-      </c>
-      <c r="O18">
-        <v>159</v>
-      </c>
-      <c r="P18">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="19" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="M19">
-        <v>175</v>
-      </c>
-      <c r="N19">
-        <v>130</v>
-      </c>
-      <c r="O19">
-        <v>159</v>
-      </c>
-      <c r="P19">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="20" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="M20">
-        <v>200</v>
-      </c>
-      <c r="N20">
-        <v>130</v>
-      </c>
-      <c r="O20">
-        <v>159</v>
-      </c>
-      <c r="P20">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="21" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="M21">
-        <v>225</v>
-      </c>
-      <c r="N21">
-        <v>130</v>
-      </c>
-      <c r="O21">
-        <v>159</v>
-      </c>
-      <c r="P21">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="22" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="M22">
-        <v>250</v>
-      </c>
-      <c r="N22">
-        <v>130</v>
-      </c>
-      <c r="O22">
-        <v>159</v>
-      </c>
-      <c r="P22">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="23" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="M23">
-        <v>275</v>
-      </c>
-      <c r="N23">
-        <v>130</v>
-      </c>
-      <c r="O23">
-        <v>159</v>
-      </c>
-      <c r="P23">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="24" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="M24">
-        <v>300</v>
-      </c>
-      <c r="N24">
-        <v>130</v>
-      </c>
-      <c r="O24">
-        <v>159</v>
-      </c>
-      <c r="P24">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="25" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="M25">
-        <v>325</v>
-      </c>
-      <c r="N25">
-        <v>130</v>
-      </c>
-      <c r="O25">
-        <v>159</v>
-      </c>
-      <c r="P25">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="26" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="M26">
-        <v>350</v>
-      </c>
-      <c r="N26">
-        <v>130</v>
-      </c>
-      <c r="O26">
-        <v>159</v>
-      </c>
-      <c r="P26">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="27" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="M27">
-        <v>375</v>
-      </c>
-      <c r="N27">
-        <v>130</v>
-      </c>
-      <c r="O27">
-        <v>158</v>
-      </c>
-      <c r="P27">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="28" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="M28">
-        <v>400</v>
-      </c>
-      <c r="N28">
-        <v>130</v>
-      </c>
-      <c r="O28">
-        <v>153</v>
-      </c>
-      <c r="P28">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="29" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="M29">
-        <v>425</v>
-      </c>
-      <c r="N29">
-        <v>125</v>
-      </c>
-      <c r="O29">
-        <v>139</v>
-      </c>
-      <c r="P29">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="30" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="M30">
-        <v>450</v>
-      </c>
-      <c r="N30">
-        <v>115</v>
-      </c>
-      <c r="O30">
-        <v>117</v>
-      </c>
-      <c r="P30">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="31" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="M31">
-        <v>475</v>
-      </c>
-      <c r="N31">
-        <v>93.7</v>
-      </c>
-      <c r="O31">
-        <v>93</v>
-      </c>
-      <c r="P31">
-        <v>92.7</v>
-      </c>
-    </row>
-    <row r="32" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="M32">
-        <v>500</v>
-      </c>
-      <c r="N32">
-        <v>68.400000000000006</v>
-      </c>
-      <c r="O32">
-        <v>68.599999999999994</v>
-      </c>
-      <c r="P32">
-        <v>68.8</v>
-      </c>
-    </row>
-    <row r="33" spans="13:16" x14ac:dyDescent="0.3">
-      <c r="M33">
-        <v>525</v>
-      </c>
-      <c r="N33">
-        <v>43.8</v>
-      </c>
-      <c r="O33">
-        <v>43.7</v>
-      </c>
-      <c r="P33">
-        <v>43.6</v>
-      </c>
-    </row>
-    <row r="34" spans="13:16" x14ac:dyDescent="0.3">
-      <c r="M34">
-        <v>550</v>
-      </c>
-      <c r="N34">
-        <v>18.899999999999999</v>
-      </c>
-      <c r="O34">
-        <v>18.899999999999999</v>
-      </c>
-      <c r="P34">
-        <v>18.899999999999999</v>
+    <row r="13" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D13" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="D13" ca="1">_xll.MatSearch("SA-516")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M13" t="e" cm="1">
+        <f t="array" aca="1" ref="M13" ca="1">_xll.MatAllowableStressTable("ASME-355","Bolting")</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="21" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D21" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="D21" ca="1">_xll.MatSearch("SA-193","B7")</f>
+        <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
